--- a/measurements/24/Filled_2D_sections/sagittal/week24_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/24/Filled_2D_sections/sagittal/week24_sagittal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,52 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,34 +546,61 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.364069006543724</v>
+        <v>1663.492063492063</v>
       </c>
       <c r="D2" t="n">
-        <v>8.692485754082844</v>
+        <v>169.7104361511412</v>
       </c>
       <c r="E2" t="n">
-        <v>8.623499727830655</v>
+        <v>168.363566114789</v>
       </c>
       <c r="F2" t="n">
-        <v>1.007999771372353</v>
+        <v>1.007999771372352</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7257942078866784</v>
+        <v>0.7257942078866786</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.237723214285714</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6.181175595238095</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.209449404761904</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6.181175595238095</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.237723214285714</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>4.610782272456872</v>
+      <c r="W2" s="2" t="n">
+        <v>1757.534013605442</v>
       </c>
     </row>
     <row r="3">
@@ -544,34 +611,61 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.441998810232005</v>
+        <v>1693.197278911565</v>
       </c>
       <c r="D3" t="n">
-        <v>8.801882880490002</v>
+        <v>171.8462848095667</v>
       </c>
       <c r="E3" t="n">
-        <v>8.753102363609687</v>
+        <v>170.8939032895224</v>
       </c>
       <c r="F3" t="n">
         <v>1.005572940296359</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7205052190042111</v>
+        <v>0.7205052190042112</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5.913318452380952</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.385230654761904</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5.913318452380952</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>9.620022170427371</v>
+      <c r="W3" s="2" t="n">
+        <v>187.8194804702486</v>
       </c>
     </row>
     <row r="4">
@@ -582,17 +676,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.515764425936942</v>
+        <v>1721.315192743764</v>
       </c>
       <c r="D4" t="n">
-        <v>8.870868900927102</v>
+        <v>173.1931547323863</v>
       </c>
       <c r="E4" t="n">
-        <v>8.787595385458411</v>
+        <v>171.5673384779975</v>
       </c>
       <c r="F4" t="n">
         <v>1.009476257362337</v>
@@ -601,15 +695,42 @@
         <v>0.7211221240859979</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.597098214285714</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.465215773809524</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5.597098214285714</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>9.107991680139449</v>
+      <c r="W4" s="2" t="n">
+        <v>177.8226947074845</v>
       </c>
     </row>
     <row r="5">
@@ -620,33 +741,60 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.578524687685902</v>
+        <v>1745.238095238095</v>
       </c>
       <c r="D5" t="n">
-        <v>8.994553481660239</v>
+        <v>175.6079489276522</v>
       </c>
       <c r="E5" t="n">
-        <v>8.896992485697677</v>
+        <v>173.7031866255261</v>
       </c>
       <c r="F5" t="n">
         <v>1.010965615191807</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7111745512348374</v>
+        <v>0.7111745512348377</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.524553571428571</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.428943452380953</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5.524553571428571</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="W5" s="2" t="n">
         <v>1.055140834431625</v>
       </c>
     </row>
@@ -658,33 +806,60 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.578524687685902</v>
+        <v>1745.238095238095</v>
       </c>
       <c r="D6" t="n">
-        <v>8.994553481660239</v>
+        <v>175.6079489276522</v>
       </c>
       <c r="E6" t="n">
-        <v>8.896992485697677</v>
+        <v>173.7031866255261</v>
       </c>
       <c r="F6" t="n">
         <v>1.010965615191807</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7111745512348374</v>
+        <v>0.7111745512348377</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5.524553571428571</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.428943452380953</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.524553571428571</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="W6" s="2" t="n">
         <v>0.6374605508602832</v>
       </c>
     </row>
@@ -696,34 +871,61 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.621951219512195</v>
+        <v>1761.791383219954</v>
       </c>
       <c r="D7" t="n">
-        <v>9.043333986910378</v>
+        <v>176.5603302206312</v>
       </c>
       <c r="E7" t="n">
-        <v>8.931485542436926</v>
+        <v>174.3766224951971</v>
       </c>
       <c r="F7" t="n">
         <v>1.012522938534919</v>
       </c>
       <c r="G7" t="n">
-        <v>0.710195769146497</v>
+        <v>0.7101957691464968</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.625372023809524</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.842633928571428</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.734002976190476</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5.842633928571428</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.625372023809524</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0.3</v>
+      <c r="W7" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -734,34 +936,61 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.664187983343249</v>
+        <v>1777.891156462585</v>
       </c>
       <c r="D8" t="n">
-        <v>9.112319984087129</v>
+        <v>177.9071996893202</v>
       </c>
       <c r="E8" t="n">
-        <v>9.014759014292462</v>
+        <v>176.0024378980909</v>
       </c>
       <c r="F8" t="n">
         <v>1.010822360269419</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7058753012371473</v>
+        <v>0.705875301237147</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.109002976190476</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.70126488095238</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.905133928571429</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5.70126488095238</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.109002976190476</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6475482723577236</v>
+      <c r="W8" s="2" t="n">
+        <v>5.125837053571429</v>
       </c>
     </row>
     <row r="9">
@@ -772,34 +1001,61 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4.664187983343249</v>
+        <v>1777.891156462585</v>
       </c>
       <c r="D9" t="n">
-        <v>9.112319984087129</v>
+        <v>177.9071996893202</v>
       </c>
       <c r="E9" t="n">
-        <v>9.014759014292462</v>
+        <v>176.0024378980909</v>
       </c>
       <c r="F9" t="n">
         <v>1.010822360269419</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7058753012371473</v>
+        <v>0.705875301237147</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.109002976190476</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.70126488095238</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.905133928571429</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5.70126488095238</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.109002976190476</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.6475482723577236</v>
+      <c r="W9" s="2" t="n">
+        <v>7.913318452380952</v>
       </c>
     </row>
     <row r="10">
@@ -810,17 +1066,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.70404521118382</v>
+        <v>1793.083900226757</v>
       </c>
       <c r="D10" t="n">
-        <v>9.230086518497002</v>
+        <v>180.2064510754176</v>
       </c>
       <c r="E10" t="n">
-        <v>9.124156105809096</v>
+        <v>178.1382858753204</v>
       </c>
       <c r="F10" t="n">
         <v>1.011609886049677</v>
@@ -829,15 +1085,42 @@
         <v>0.6938567336577245</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.847470238095238</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.68266369047619</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.265066964285714</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.68266369047619</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.847470238095238</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.6475482723577236</v>
+      <c r="W10" s="2" t="n">
+        <v>6.51957775297619</v>
       </c>
     </row>
     <row r="11">
@@ -848,26 +1131,61 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.733194527067222</v>
+        <v>1804.195011337868</v>
       </c>
       <c r="D11" t="n">
-        <v>9.319278054121064</v>
+        <v>181.9478096280779</v>
       </c>
       <c r="E11" t="n">
-        <v>9.138443586302968</v>
+        <v>178.4172319230579</v>
       </c>
       <c r="F11" t="n">
         <v>1.019788322388852</v>
       </c>
       <c r="G11" t="n">
-        <v>0.684856651724389</v>
+        <v>0.6848566517243889</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.33110119047619</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.907738095238095</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.619419642857142</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5.907738095238095</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5.33110119047619</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="12">
@@ -878,26 +1196,61 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4.733194527067222</v>
+        <v>1804.195011337868</v>
       </c>
       <c r="D12" t="n">
-        <v>9.319278054121064</v>
+        <v>181.9478096280779</v>
       </c>
       <c r="E12" t="n">
-        <v>9.138443586302968</v>
+        <v>178.4172319230579</v>
       </c>
       <c r="F12" t="n">
         <v>1.019788322388852</v>
       </c>
       <c r="G12" t="n">
-        <v>0.684856651724389</v>
+        <v>0.6848566517243889</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5.33110119047619</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.907738095238095</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.619419642857142</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5.907738095238095</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5.33110119047619</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>12.64260912698412</v>
       </c>
     </row>
     <row r="13">
@@ -908,17 +1261,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.750743604997026</v>
+        <v>1810.884353741496</v>
       </c>
       <c r="D13" t="n">
-        <v>9.3419349193573</v>
+        <v>182.3901579493568</v>
       </c>
       <c r="E13" t="n">
-        <v>9.187224056662583</v>
+        <v>179.3696125348409</v>
       </c>
       <c r="F13" t="n">
         <v>1.016839783349196</v>
@@ -927,7 +1280,42 @@
         <v>0.6840656475510488</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.792410714285714</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.931919642857142</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.862165178571428</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5.931919642857142</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5.792410714285714</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="14">
@@ -938,26 +1326,61 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.760559190957763</v>
+        <v>1814.625850340136</v>
       </c>
       <c r="D14" t="n">
-        <v>9.546441662602309</v>
+        <v>186.382908650807</v>
       </c>
       <c r="E14" t="n">
-        <v>9.253758753218301</v>
+        <v>180.6686232771192</v>
       </c>
       <c r="F14" t="n">
         <v>1.031628543296768</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6564245082022258</v>
+        <v>0.6564245082022259</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.2890625</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6.497395833333333</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.393229166666666</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>6.497395833333333</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6.2890625</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>6.205450148809524</v>
       </c>
     </row>
     <row r="15">
@@ -968,26 +1391,61 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.760559190957763</v>
+        <v>1814.625850340136</v>
       </c>
       <c r="D15" t="n">
-        <v>9.546441662602309</v>
+        <v>186.382908650807</v>
       </c>
       <c r="E15" t="n">
-        <v>9.253758753218301</v>
+        <v>180.6686232771192</v>
       </c>
       <c r="F15" t="n">
         <v>1.031628543296768</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6564245082022258</v>
+        <v>0.6564245082022259</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6.2890625</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6.497395833333333</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6.393229166666666</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>6.497395833333333</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6.2890625</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="n">
+        <v>4.643632192460317</v>
       </c>
     </row>
     <row r="16">
@@ -998,35 +1456,61 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.654074955383701</v>
+        <v>1774.036281179138</v>
       </c>
       <c r="D16" t="n">
-        <v>10.97637865892271</v>
+        <v>214.3007261980148</v>
       </c>
       <c r="E16" t="n">
-        <v>9.282333705483413</v>
+        <v>181.2265152022952</v>
       </c>
       <c r="F16" t="n">
         <v>1.1825020525214</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4854282824599853</v>
+        <v>0.4854282824599852</v>
       </c>
       <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6.880580357142857</v>
+      </c>
+      <c r="J16" t="n">
+        <v>11.19977678571428</v>
+      </c>
+      <c r="K16" t="n">
+        <v>9.040178571428571</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.5736471036585366</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.5736471036585366</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.5736471036585366</v>
+      <c r="M16" t="n">
+        <v>11.19977678571428</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>6.880580357142857</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="17">
@@ -1037,35 +1521,61 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.604104699583582</v>
+        <v>1754.988662131519</v>
       </c>
       <c r="D17" t="n">
-        <v>10.85861211288266</v>
+        <v>212.0014745848519</v>
       </c>
       <c r="E17" t="n">
-        <v>9.262128161221016</v>
+        <v>180.8320260047913</v>
       </c>
       <c r="F17" t="n">
         <v>1.172366860388075</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4906891055687506</v>
+        <v>0.4906891055687504</v>
       </c>
       <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7.018229166666666</v>
+      </c>
+      <c r="J17" t="n">
+        <v>11.98846726190476</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9.503348214285714</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.6140434451219512</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.6140434451219512</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.6140434451219512</v>
+      <c r="M17" t="n">
+        <v>11.98846726190476</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>7.018229166666666</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="n">
+        <v>2.547433035714286</v>
       </c>
     </row>
     <row r="18">
@@ -1076,35 +1586,61 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.604104699583582</v>
+        <v>1754.988662131519</v>
       </c>
       <c r="D18" t="n">
-        <v>10.85861211288266</v>
+        <v>212.0014745848519</v>
       </c>
       <c r="E18" t="n">
-        <v>9.262128161221016</v>
+        <v>180.8320260047913</v>
       </c>
       <c r="F18" t="n">
         <v>1.172366860388075</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4906891055687506</v>
+        <v>0.4906891055687504</v>
       </c>
       <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7.018229166666666</v>
+      </c>
+      <c r="J18" t="n">
+        <v>11.98846726190476</v>
+      </c>
+      <c r="K18" t="n">
+        <v>9.503348214285714</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.6140434451219512</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.6140434451219512</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.6140434451219512</v>
+      <c r="M18" t="n">
+        <v>11.98846726190476</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>7.018229166666666</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1115,35 +1651,53 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.55026769779893</v>
+        <v>1734.467120181406</v>
       </c>
       <c r="D19" t="n">
-        <v>10.81574972373683</v>
+        <v>211.1646374634334</v>
       </c>
       <c r="E19" t="n">
-        <v>9.331114190380749</v>
+        <v>182.1788960979098</v>
       </c>
       <c r="F19" t="n">
         <v>1.159105922729631</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4888026516671929</v>
+        <v>0.4888026516671928</v>
       </c>
       <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6.919642857142857</v>
+      </c>
+      <c r="J19" t="n">
+        <v>12.75111607142857</v>
+      </c>
+      <c r="K19" t="n">
+        <v>9.835379464285714</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.6531059451219512</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.6531059451219512</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.6531059451219512</v>
+      <c r="M19" t="n">
+        <v>12.75111607142857</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>6.919642857142857</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1154,17 +1708,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.465794170136824</v>
+        <v>1702.267573696145</v>
       </c>
       <c r="D20" t="n">
-        <v>10.48265573745821</v>
+        <v>204.6613739218031</v>
       </c>
       <c r="E20" t="n">
-        <v>9.503579261826307</v>
+        <v>185.5460713023231</v>
       </c>
       <c r="F20" t="n">
         <v>1.103021866673394</v>
@@ -1173,16 +1727,34 @@
         <v>0.5107000729058139</v>
       </c>
       <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.930803571428571</v>
+      </c>
+      <c r="J20" t="n">
+        <v>13.96391369047619</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10.44735863095238</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.7152248475609756</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.7152248475609756</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.7152248475609756</v>
+      <c r="M20" t="n">
+        <v>13.96391369047619</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>6.930803571428571</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1193,17 +1765,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.465794170136824</v>
+        <v>1702.267573696145</v>
       </c>
       <c r="D21" t="n">
-        <v>10.48265573745821</v>
+        <v>204.6613739218031</v>
       </c>
       <c r="E21" t="n">
-        <v>9.503579261826307</v>
+        <v>185.5460713023231</v>
       </c>
       <c r="F21" t="n">
         <v>1.103021866673394</v>
@@ -1212,16 +1784,34 @@
         <v>0.5107000729058139</v>
       </c>
       <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.930803571428571</v>
+      </c>
+      <c r="J21" t="n">
+        <v>13.96391369047619</v>
+      </c>
+      <c r="K21" t="n">
+        <v>10.44735863095238</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.7152248475609756</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.7152248475609756</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.7152248475609756</v>
+      <c r="M21" t="n">
+        <v>13.96391369047619</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>6.930803571428571</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1231,7 +1821,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
       </c>
     </row>
     <row r="23">
@@ -1254,6 +1844,38 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/24/Filled_2D_sections/sagittal/week24_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/24/Filled_2D_sections/sagittal/week24_sagittal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1881,4 +2087,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week24_sagittal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1757.534013605442</v>
+      </c>
+      <c r="D10" t="n">
+        <v>44.33951951771729</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1663.492063492063</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1814.625850340136</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>187.8194804702486</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15.49555690708076</v>
+      </c>
+      <c r="E11" t="n">
+        <v>169.7104361511412</v>
+      </c>
+      <c r="F11" t="n">
+        <v>214.3007261980148</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.055140834431625</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.06588578915639971</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.005572940296359</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.1825020525214</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6374605508602833</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.09684913079607557</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4854282824599852</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7257942078866786</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis0_s00_idx0062.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis0_s01_idx0063.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis0_s02_idx0064.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis0_s03_idx0065.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis0_s04_idx0065.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis0_s05_idx0066.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis0_s06_idx0067.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis0_s07_idx0067.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis0_s08_idx0068.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis0_s09_idx0069.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis0_s10_idx0069.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis0_s11_idx0070.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis0_s12_idx0071.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis0_s13_idx0071.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis0_s14_idx0072.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis0_s15_idx0073.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis0_s16_idx0073.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis0_s17_idx0074.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis0_s18_idx0075.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis0_s19_idx0075.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4701623459816272</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.5026246899500346</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.3077935056255462</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>6</v>
+      </c>
+      <c r="C48" t="n">
+        <v>12.64260912698412</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.134991945373695</v>
+      </c>
+      <c r="E48" t="n">
+        <v>11.19977678571428</v>
+      </c>
+      <c r="F48" t="n">
+        <v>13.96391369047619</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>32</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5.619768415178571</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.119239379269614</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7.018229166666666</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.547433035714286</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.4379958298644354</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.237723214285714</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.857142857142857</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>